--- a/class7.xlsx
+++ b/class7.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D3\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25032739-94FC-4492-8DF8-E2A03B7A1F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C15BE9D-BA70-4F21-B664-66D8D486EC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12705" yWindow="2535" windowWidth="15360" windowHeight="14685" xr2:uid="{CA5E7D9E-C1AD-403B-9234-9F3A5FCAD358}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CA5E7D9E-C1AD-403B-9234-9F3A5FCAD358}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
   <si>
     <t>Roll No</t>
   </si>
@@ -76,6 +79,24 @@
   </si>
   <si>
     <t>Sneha</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Pen</t>
+  </si>
+  <si>
+    <t>Pencil</t>
+  </si>
+  <si>
+    <t>Eraser</t>
+  </si>
+  <si>
+    <t>Scale</t>
   </si>
 </sst>
 </file>
@@ -580,4 +601,154 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B075061-BF2C-4BEA-88A1-8AA47150FBCD}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26355F7B-9226-4B78-A20C-29B42FCD1FD0}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D69218C-E9D2-4676-833D-CEAA908AF015}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/class7.xlsx
+++ b/class7.xlsx
@@ -5,18 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D3\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\class 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C15BE9D-BA70-4F21-B664-66D8D486EC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57843D3-F5A0-4A3D-8F5E-78EBA17CB532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CA5E7D9E-C1AD-403B-9234-9F3A5FCAD358}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{754137B3-23C5-4B7F-94ED-D0B0810EA8EC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Class A" sheetId="1" r:id="rId1"/>
+    <sheet name="Class B" sheetId="2" r:id="rId2"/>
+    <sheet name="Class C" sheetId="3" r:id="rId3"/>
+    <sheet name="Summary" sheetId="4" r:id="rId4"/>
+    <sheet name="Combo chart" sheetId="6" r:id="rId5"/>
+    <sheet name="Sparkline" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,9 +42,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
-  <si>
-    <t>Roll No</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
+  <si>
+    <t>Subject - Science</t>
   </si>
   <si>
     <t>Student Name</t>
@@ -51,59 +53,107 @@
     <t>Marks</t>
   </si>
   <si>
-    <t>Ravi</t>
-  </si>
-  <si>
-    <t>Aman</t>
+    <t>Aanya</t>
+  </si>
+  <si>
+    <t>Rohan</t>
+  </si>
+  <si>
+    <t>Prerna</t>
+  </si>
+  <si>
+    <t>Kabir</t>
+  </si>
+  <si>
+    <t>Subject - Maths</t>
+  </si>
+  <si>
+    <t>Subject - Computer</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>Rahul</t>
   </si>
   <si>
     <t>Priya</t>
   </si>
   <si>
+    <t>Amit</t>
+  </si>
+  <si>
     <t>Neha</t>
   </si>
   <si>
-    <t>Rahul</t>
+    <t>Arjun</t>
+  </si>
+  <si>
+    <t>Sneha</t>
+  </si>
+  <si>
+    <t>Karan</t>
+  </si>
+  <si>
+    <t>Pooja</t>
+  </si>
+  <si>
+    <t>Vivek</t>
   </si>
   <si>
     <t>Anjali</t>
   </si>
   <si>
-    <t>Vikram</t>
-  </si>
-  <si>
-    <t>Pooja</t>
-  </si>
-  <si>
-    <t>Karan</t>
-  </si>
-  <si>
-    <t>Sneha</t>
-  </si>
-  <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>Sales</t>
-  </si>
-  <si>
-    <t>Pen</t>
-  </si>
-  <si>
-    <t>Pencil</t>
-  </si>
-  <si>
-    <t>Eraser</t>
-  </si>
-  <si>
-    <t>Scale</t>
+    <t>Sparkline</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-14009]dd/mm/yyyy;@"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,8 +169,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -129,12 +186,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -142,22 +211,97 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -175,6 +319,1077 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combo chart'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Combo chart'!$A$2:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Combo chart'!$B$2:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>21000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>23000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>35000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5121-4A41-B93B-75DBE17E562A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="100"/>
+        <c:axId val="1552220047"/>
+        <c:axId val="1552220879"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combo chart'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Profit</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Combo chart'!$A$2:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Combo chart'!$C$2:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2400</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3200</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3700</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5121-4A41-B93B-75DBE17E562A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1552220047"/>
+        <c:axId val="1552220879"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1552220047"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1552220879"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1552220879"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1552220047"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5458F3EB-0EFD-43E5-9682-A2BE37DAB94D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -473,282 +1688,894 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44A6D564-867F-4AE4-9D0F-B078ACAFCEA1}">
-  <dimension ref="A1:C11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1EDCA96-B232-4456-8863-0BF7F6F0C1D8}">
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>101</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1">
+      <c r="B3" s="6"/>
+      <c r="C3" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>102</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>103</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>104</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>105</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>106</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="1">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>107</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>108</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>109</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="1">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>110</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="1">
-        <v>76</v>
-      </c>
-    </row>
   </sheetData>
+  <dataConsolidate/>
+  <mergeCells count="6">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B075061-BF2C-4BEA-88A1-8AA47150FBCD}">
-  <dimension ref="A1:B5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8719D534-0C2B-4096-A98F-015F5C933939}">
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="1">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="1">
-        <v>60</v>
+        <v>7</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="1">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26355F7B-9226-4B78-A20C-29B42FCD1FD0}">
-  <dimension ref="A1:B5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FA7CFB-504E-437A-9774-A5580264A784}">
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="1">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="1">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="1">
+        <v>8</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="1">
-        <v>70</v>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="1">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D69218C-E9D2-4676-833D-CEAA908AF015}">
-  <dimension ref="A1:B5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C19CDD78-B41E-40EC-8550-9BFFE8B6B411}">
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="1">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="1">
+        <v>220</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataConsolidate>
+    <dataRefs count="3">
+      <dataRef ref="C3:C6" sheet="Class A"/>
+      <dataRef ref="C3:C6" sheet="Class B"/>
+      <dataRef ref="C3:C6" sheet="Class C"/>
+    </dataRefs>
+  </dataConsolidate>
+  <mergeCells count="6">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA8A8C44-2B40-404E-8F95-FA148C41EB64}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="16">
+        <v>12000</v>
+      </c>
+      <c r="C2" s="16">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B3" s="16">
+        <v>15000</v>
+      </c>
+      <c r="C3" s="16">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B4" s="16">
+        <v>18000</v>
+      </c>
+      <c r="C4" s="16">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="1">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B5" s="16">
+        <v>16000</v>
+      </c>
+      <c r="C5" s="16">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="1">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B6" s="16">
+        <v>21000</v>
+      </c>
+      <c r="C6" s="16">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="1">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B7" s="16">
+        <v>25000</v>
+      </c>
+      <c r="C7" s="16">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="1">
-        <v>75</v>
+      <c r="B8" s="16">
+        <v>23000</v>
+      </c>
+      <c r="C8" s="16">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="16">
+        <v>28000</v>
+      </c>
+      <c r="C9" s="16">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="16">
+        <v>30000</v>
+      </c>
+      <c r="C10" s="16">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="16">
+        <v>35000</v>
+      </c>
+      <c r="C11" s="16">
+        <v>6000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBE605A4-1C70-43CC-ADDF-41911F773390}">
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="12" max="12" width="17.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="16">
+        <v>45</v>
+      </c>
+      <c r="C2" s="16">
+        <v>52</v>
+      </c>
+      <c r="D2" s="16">
+        <v>48</v>
+      </c>
+      <c r="E2" s="16">
+        <v>60</v>
+      </c>
+      <c r="F2" s="16">
+        <v>58</v>
+      </c>
+      <c r="G2" s="16">
+        <v>65</v>
+      </c>
+      <c r="H2" s="16">
+        <v>70</v>
+      </c>
+      <c r="I2" s="16">
+        <v>68</v>
+      </c>
+      <c r="J2" s="16">
+        <v>75</v>
+      </c>
+      <c r="K2" s="16">
+        <v>80</v>
+      </c>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="16">
+        <v>55</v>
+      </c>
+      <c r="C3" s="16">
+        <v>58</v>
+      </c>
+      <c r="D3" s="16">
+        <v>62</v>
+      </c>
+      <c r="E3" s="16">
+        <v>60</v>
+      </c>
+      <c r="F3" s="16">
+        <v>64</v>
+      </c>
+      <c r="G3" s="16">
+        <v>68</v>
+      </c>
+      <c r="H3" s="16">
+        <v>72</v>
+      </c>
+      <c r="I3" s="16">
+        <v>70</v>
+      </c>
+      <c r="J3" s="16">
+        <v>74</v>
+      </c>
+      <c r="K3" s="16">
+        <v>78</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="16">
+        <v>35</v>
+      </c>
+      <c r="C4" s="16">
+        <v>40</v>
+      </c>
+      <c r="D4" s="16">
+        <v>38</v>
+      </c>
+      <c r="E4" s="16">
+        <v>45</v>
+      </c>
+      <c r="F4" s="16">
+        <v>50</v>
+      </c>
+      <c r="G4" s="16">
+        <v>48</v>
+      </c>
+      <c r="H4" s="16">
+        <v>55</v>
+      </c>
+      <c r="I4" s="16">
+        <v>60</v>
+      </c>
+      <c r="J4" s="16">
+        <v>58</v>
+      </c>
+      <c r="K4" s="16">
+        <v>65</v>
+      </c>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="16">
+        <v>60</v>
+      </c>
+      <c r="C5" s="16">
+        <v>62</v>
+      </c>
+      <c r="D5" s="16">
+        <v>65</v>
+      </c>
+      <c r="E5" s="16">
+        <v>68</v>
+      </c>
+      <c r="F5" s="16">
+        <v>70</v>
+      </c>
+      <c r="G5" s="16">
+        <v>72</v>
+      </c>
+      <c r="H5" s="16">
+        <v>75</v>
+      </c>
+      <c r="I5" s="16">
+        <v>78</v>
+      </c>
+      <c r="J5" s="16">
+        <v>80</v>
+      </c>
+      <c r="K5" s="16">
+        <v>85</v>
+      </c>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="16">
+        <v>50</v>
+      </c>
+      <c r="C6" s="16">
+        <v>48</v>
+      </c>
+      <c r="D6" s="16">
+        <v>52</v>
+      </c>
+      <c r="E6" s="16">
+        <v>55</v>
+      </c>
+      <c r="F6" s="16">
+        <v>58</v>
+      </c>
+      <c r="G6" s="16">
+        <v>60</v>
+      </c>
+      <c r="H6" s="16">
+        <v>62</v>
+      </c>
+      <c r="I6" s="16">
+        <v>65</v>
+      </c>
+      <c r="J6" s="16">
+        <v>68</v>
+      </c>
+      <c r="K6" s="16">
+        <v>70</v>
+      </c>
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="16">
+        <v>42</v>
+      </c>
+      <c r="C7" s="16">
+        <v>45</v>
+      </c>
+      <c r="D7" s="16">
+        <v>50</v>
+      </c>
+      <c r="E7" s="16">
+        <v>55</v>
+      </c>
+      <c r="F7" s="16">
+        <v>53</v>
+      </c>
+      <c r="G7" s="16">
+        <v>58</v>
+      </c>
+      <c r="H7" s="16">
+        <v>60</v>
+      </c>
+      <c r="I7" s="16">
+        <v>64</v>
+      </c>
+      <c r="J7" s="16">
+        <v>66</v>
+      </c>
+      <c r="K7" s="16">
+        <v>72</v>
+      </c>
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="16">
+        <v>38</v>
+      </c>
+      <c r="C8" s="16">
+        <v>42</v>
+      </c>
+      <c r="D8" s="16">
+        <v>45</v>
+      </c>
+      <c r="E8" s="16">
+        <v>48</v>
+      </c>
+      <c r="F8" s="16">
+        <v>52</v>
+      </c>
+      <c r="G8" s="16">
+        <v>55</v>
+      </c>
+      <c r="H8" s="16">
+        <v>58</v>
+      </c>
+      <c r="I8" s="16">
+        <v>60</v>
+      </c>
+      <c r="J8" s="16">
+        <v>63</v>
+      </c>
+      <c r="K8" s="16">
+        <v>67</v>
+      </c>
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="16">
+        <v>65</v>
+      </c>
+      <c r="C9" s="16">
+        <v>68</v>
+      </c>
+      <c r="D9" s="16">
+        <v>70</v>
+      </c>
+      <c r="E9" s="16">
+        <v>72</v>
+      </c>
+      <c r="F9" s="16">
+        <v>75</v>
+      </c>
+      <c r="G9" s="16">
+        <v>78</v>
+      </c>
+      <c r="H9" s="16">
+        <v>80</v>
+      </c>
+      <c r="I9" s="16">
+        <v>82</v>
+      </c>
+      <c r="J9" s="16">
+        <v>85</v>
+      </c>
+      <c r="K9" s="16">
+        <v>88</v>
+      </c>
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="16">
+        <v>48</v>
+      </c>
+      <c r="C10" s="16">
+        <v>50</v>
+      </c>
+      <c r="D10" s="16">
+        <v>55</v>
+      </c>
+      <c r="E10" s="16">
+        <v>53</v>
+      </c>
+      <c r="F10" s="16">
+        <v>58</v>
+      </c>
+      <c r="G10" s="16">
+        <v>60</v>
+      </c>
+      <c r="H10" s="16">
+        <v>65</v>
+      </c>
+      <c r="I10" s="16">
+        <v>68</v>
+      </c>
+      <c r="J10" s="16">
+        <v>70</v>
+      </c>
+      <c r="K10" s="16">
+        <v>74</v>
+      </c>
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="16">
+        <v>58</v>
+      </c>
+      <c r="C11" s="16">
+        <v>60</v>
+      </c>
+      <c r="D11" s="16">
+        <v>62</v>
+      </c>
+      <c r="E11" s="16">
+        <v>65</v>
+      </c>
+      <c r="F11" s="16">
+        <v>67</v>
+      </c>
+      <c r="G11" s="16">
+        <v>70</v>
+      </c>
+      <c r="H11" s="16">
+        <v>72</v>
+      </c>
+      <c r="I11" s="16">
+        <v>75</v>
+      </c>
+      <c r="J11" s="16">
+        <v>78</v>
+      </c>
+      <c r="K11" s="16">
+        <v>82</v>
+      </c>
+      <c r="L11" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
+      <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{BAA06611-EC97-4DE1-A464-1AD0764C436B}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sparkline!A2:K2</xm:f>
+              <xm:sqref>L2</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sparkline!A3:K3</xm:f>
+              <xm:sqref>L3</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sparkline!A4:K4</xm:f>
+              <xm:sqref>L4</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sparkline!A5:K5</xm:f>
+              <xm:sqref>L5</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sparkline!A6:K6</xm:f>
+              <xm:sqref>L6</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sparkline!A7:K7</xm:f>
+              <xm:sqref>L7</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sparkline!A8:K8</xm:f>
+              <xm:sqref>L8</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sparkline!A9:K9</xm:f>
+              <xm:sqref>L9</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sparkline!A10:K10</xm:f>
+              <xm:sqref>L10</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sparkline!A11:K11</xm:f>
+              <xm:sqref>L11</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+      </x14:sparklineGroups>
+    </ext>
+  </extLst>
 </worksheet>
 </file>